--- a/examples/convert/mwtab/Saved Directives/mwtab_nmr_binned_conversion_directives.xlsx
+++ b/examples/convert/mwtab/Saved Directives/mwtab_nmr_binned_conversion_directives.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="133">
   <si>
     <t>#tags</t>
   </si>
@@ -271,7 +271,7 @@
     <t>;</t>
   </si>
   <si>
-    <t>NM</t>
+    <t>NMR</t>
   </si>
   <si>
     <t>acquisition_time," ",acquisition_time%units</t>
@@ -346,36 +346,39 @@
     <t>False</t>
   </si>
   <si>
+    <t>#.fill_headers</t>
+  </si>
+  <si>
+    <t>#.table</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>entity</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>protocol</t>
+  </si>
+  <si>
+    <t>#.for_each</t>
+  </si>
+  <si>
+    <t>measurement</t>
+  </si>
+  <si>
     <t>*#.headers</t>
   </si>
   <si>
     <t>"Bin range(ppm)"=assignment,entity.id=intensity</t>
   </si>
   <si>
-    <t>#.table</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>study</t>
-  </si>
-  <si>
-    <t>entity</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t>protocol</t>
-  </si>
-  <si>
-    <t>#.for_each</t>
-  </si>
-  <si>
-    <t>measurement</t>
-  </si>
-  <si>
     <t>#.test</t>
   </si>
   <si>
@@ -400,13 +403,13 @@
     <t>ascending</t>
   </si>
   <si>
+    <t>type=treatment</t>
+  </si>
+  <si>
+    <t>type=sample_prep</t>
+  </si>
+  <si>
     <t>matrix</t>
-  </si>
-  <si>
-    <t>type=treatment</t>
-  </si>
-  <si>
-    <t>type=sample_prep</t>
   </si>
   <si>
     <t>#.values_to_str</t>
@@ -830,7 +833,7 @@
         <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s">
         <v>105</v>
@@ -847,7 +850,7 @@
         <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s">
         <v>106</v>
@@ -864,7 +867,7 @@
         <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
         <v>106</v>
@@ -881,7 +884,7 @@
         <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
         <v>106</v>
@@ -898,7 +901,7 @@
         <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F13" t="s">
         <v>106</v>
@@ -915,7 +918,7 @@
         <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F14" t="s">
         <v>106</v>
@@ -932,7 +935,7 @@
         <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F15" t="s">
         <v>106</v>
@@ -949,7 +952,7 @@
         <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F16" t="s">
         <v>106</v>
@@ -966,7 +969,7 @@
         <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
         <v>106</v>
@@ -983,7 +986,7 @@
         <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
         <v>106</v>
@@ -1003,7 +1006,7 @@
         <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
         <v>105</v>
@@ -1020,7 +1023,7 @@
         <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
         <v>106</v>
@@ -1037,7 +1040,7 @@
         <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
         <v>106</v>
@@ -1054,7 +1057,7 @@
         <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
         <v>106</v>
@@ -1071,7 +1074,7 @@
         <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
         <v>106</v>
@@ -1088,7 +1091,7 @@
         <v>108</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
         <v>106</v>
@@ -1105,7 +1108,7 @@
         <v>108</v>
       </c>
       <c r="E26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
         <v>106</v>
@@ -1122,7 +1125,7 @@
         <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
         <v>106</v>
@@ -1139,7 +1142,7 @@
         <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
         <v>106</v>
@@ -1156,7 +1159,7 @@
         <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
         <v>106</v>
@@ -1176,10 +1179,10 @@
         <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G31" t="s">
         <v>105</v>
@@ -1196,10 +1199,10 @@
         <v>108</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G32" t="s">
         <v>106</v>
@@ -1216,10 +1219,10 @@
         <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G33" t="s">
         <v>106</v>
@@ -1236,10 +1239,10 @@
         <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G34" t="s">
         <v>106</v>
@@ -1273,7 +1276,7 @@
         <v>108</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1290,10 +1293,10 @@
         <v>107</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G39" t="s">
         <v>105</v>
@@ -1310,10 +1313,10 @@
         <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G40" t="s">
         <v>106</v>
@@ -1330,10 +1333,10 @@
         <v>108</v>
       </c>
       <c r="E41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G41" t="s">
         <v>106</v>
@@ -1350,10 +1353,10 @@
         <v>108</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F42" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G42" t="s">
         <v>106</v>
@@ -1370,10 +1373,10 @@
         <v>108</v>
       </c>
       <c r="E43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G43" t="s">
         <v>106</v>
@@ -1393,22 +1396,22 @@
         <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F45" t="s">
         <v>107</v>
       </c>
       <c r="G45" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H45" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K45" t="s">
         <v>105</v>
@@ -1434,10 +1437,10 @@
         <v>81</v>
       </c>
       <c r="H46" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J46" t="s">
         <v>129</v>
@@ -1466,10 +1469,10 @@
         <v>81</v>
       </c>
       <c r="H47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J47" t="s">
         <v>129</v>
@@ -1498,10 +1501,10 @@
         <v>81</v>
       </c>
       <c r="H48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J48" t="s">
         <v>129</v>
@@ -1524,22 +1527,22 @@
         <v>66</v>
       </c>
       <c r="E50" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
         <v>107</v>
       </c>
       <c r="G50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J50" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K50" t="s">
         <v>105</v>
@@ -1562,13 +1565,13 @@
         <v>109</v>
       </c>
       <c r="G51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J51" t="s">
         <v>130</v>
@@ -1594,13 +1597,13 @@
         <v>108</v>
       </c>
       <c r="G52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J52" t="s">
         <v>130</v>
@@ -1626,13 +1629,13 @@
         <v>108</v>
       </c>
       <c r="G53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H53" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J53" t="s">
         <v>130</v>
@@ -1680,10 +1683,10 @@
         <v>107</v>
       </c>
       <c r="E58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G58" t="s">
         <v>105</v>
@@ -1700,10 +1703,10 @@
         <v>109</v>
       </c>
       <c r="E59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G59" t="s">
         <v>106</v>
@@ -1720,10 +1723,10 @@
         <v>109</v>
       </c>
       <c r="E60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F60" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G60" t="s">
         <v>106</v>
@@ -1740,10 +1743,10 @@
         <v>109</v>
       </c>
       <c r="E61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G61" t="s">
         <v>106</v>
@@ -1760,10 +1763,10 @@
         <v>108</v>
       </c>
       <c r="E62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G62" t="s">
         <v>106</v>
@@ -1780,10 +1783,10 @@
         <v>108</v>
       </c>
       <c r="E63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G63" t="s">
         <v>106</v>
@@ -1800,16 +1803,16 @@
         <v>108</v>
       </c>
       <c r="E64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G64" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:11">
       <c r="B65" t="s">
         <v>47</v>
       </c>
@@ -1820,16 +1823,16 @@
         <v>109</v>
       </c>
       <c r="E65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G65" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:11">
       <c r="B66" t="s">
         <v>48</v>
       </c>
@@ -1840,16 +1843,16 @@
         <v>109</v>
       </c>
       <c r="E66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F66" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G66" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:11">
       <c r="B67" t="s">
         <v>49</v>
       </c>
@@ -1860,16 +1863,16 @@
         <v>109</v>
       </c>
       <c r="E67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G67" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:11">
       <c r="B68" t="s">
         <v>50</v>
       </c>
@@ -1880,16 +1883,16 @@
         <v>109</v>
       </c>
       <c r="E68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G68" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:11">
       <c r="B69" t="s">
         <v>51</v>
       </c>
@@ -1900,16 +1903,16 @@
         <v>109</v>
       </c>
       <c r="E69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G69" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:11">
       <c r="B70" t="s">
         <v>52</v>
       </c>
@@ -1920,16 +1923,16 @@
         <v>109</v>
       </c>
       <c r="E70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G70" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:11">
       <c r="B71" t="s">
         <v>53</v>
       </c>
@@ -1940,16 +1943,16 @@
         <v>108</v>
       </c>
       <c r="E71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G71" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:11">
       <c r="B72" t="s">
         <v>54</v>
       </c>
@@ -1960,16 +1963,16 @@
         <v>109</v>
       </c>
       <c r="E72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F72" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G72" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:11">
       <c r="B73" t="s">
         <v>55</v>
       </c>
@@ -1980,16 +1983,16 @@
         <v>109</v>
       </c>
       <c r="E73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G73" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:11">
       <c r="B74" t="s">
         <v>56</v>
       </c>
@@ -2000,16 +2003,16 @@
         <v>109</v>
       </c>
       <c r="E74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F74" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G74" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -2023,13 +2026,13 @@
         <v>107</v>
       </c>
       <c r="E76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F76" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:11">
       <c r="B77" t="s">
         <v>58</v>
       </c>
@@ -2040,13 +2043,13 @@
         <v>108</v>
       </c>
       <c r="E77" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F77" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2060,50 +2063,53 @@
         <v>110</v>
       </c>
       <c r="E79" t="s">
+        <v>119</v>
+      </c>
+      <c r="F79" t="s">
         <v>107</v>
       </c>
-      <c r="F79" t="s">
-        <v>124</v>
-      </c>
       <c r="G79" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H79" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I79" t="s">
+        <v>111</v>
+      </c>
+      <c r="J79" t="s">
         <v>105</v>
       </c>
-      <c r="J79" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="K79" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="B80" t="s">
         <v>59</v>
       </c>
       <c r="C80" t="s">
         <v>104</v>
       </c>
-      <c r="D80" t="s">
-        <v>111</v>
-      </c>
       <c r="E80" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F80" t="s">
+        <v>108</v>
+      </c>
+      <c r="G80" t="s">
         <v>104</v>
       </c>
-      <c r="G80" t="s">
-        <v>127</v>
-      </c>
       <c r="H80" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I80" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="J80" t="s">
+        <v>131</v>
+      </c>
+      <c r="K80" t="s">
         <v>108</v>
       </c>
     </row>
